--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-medikation-atc.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-medikation-atc.xlsx
@@ -15,12 +15,13 @@
     <sheet name="Include #5" r:id="rId9" sheetId="7"/>
     <sheet name="Include #6" r:id="rId10" sheetId="8"/>
     <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -91,7 +92,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Enthaelt ATC-Codes der Versionen 2018 bis 2024</t>
+    <t>Enthaelt ATC-Codes der Versionen 2018 bis 2026</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +101,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>WHO, BfArM 1994 - 2025 - Die Erstellung erfolgt unter Verwendung der maschinenlesbaren Fassung des Bundesinstituts für Arzneimittel und Medizinprodukte (BfArM).</t>
+    <t>WHO, BfArM 1994 - 2026 - Die Erstellung erfolgt unter Verwendung der maschinenlesbaren Fassung des Bundesinstituts für Arzneimittel und Medizinprodukte (BfArM).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -385,6 +386,46 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
